--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487061_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487061_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.964700000000001</v>
+        <v>8.2613</v>
       </c>
       <c r="E2" t="n">
-        <v>8.6661</v>
+        <v>7.1233</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2986</v>
+        <v>1.138</v>
       </c>
       <c r="G2" t="n">
         <v>5.1571</v>
@@ -610,13 +610,13 @@
         <v>2.5091</v>
       </c>
       <c r="S2" t="n">
-        <v>3.8258</v>
+        <v>2.1224</v>
       </c>
       <c r="T2" t="n">
-        <v>3.8258</v>
+        <v>2.2831</v>
       </c>
       <c r="U2" t="n">
-        <v>-0</v>
+        <v>-0.1607</v>
       </c>
       <c r="V2" t="n">
         <v>3.6839</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2489</v>
+        <v>-0.7351</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5718</v>
+        <v>1.5878</v>
       </c>
       <c r="F3" t="n">
         <v>-2.3229</v>
@@ -688,10 +688,10 @@
         <v>2.1231</v>
       </c>
       <c r="S3" t="n">
-        <v>3.0564</v>
+        <v>1.0725</v>
       </c>
       <c r="T3" t="n">
-        <v>3.3803</v>
+        <v>1.3964</v>
       </c>
       <c r="U3" t="n">
         <v>-0.3239</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.8227</v>
+        <v>-0.8316</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3185</v>
+        <v>0.7379</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.1412</v>
+        <v>-1.5695</v>
       </c>
       <c r="G4" t="n">
         <v>-1.6777</v>
@@ -766,13 +766,13 @@
         <v>1.5441</v>
       </c>
       <c r="S4" t="n">
-        <v>1.9129</v>
+        <v>1.904</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9029</v>
+        <v>1.3223</v>
       </c>
       <c r="U4" t="n">
-        <v>1.0099</v>
+        <v>0.5816</v>
       </c>
       <c r="V4" t="n">
         <v>-0.2859</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.486</v>
+        <v>-1.2521</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1145</v>
+        <v>0.2146</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.6005</v>
+        <v>-1.4667</v>
       </c>
       <c r="G5" t="n">
         <v>-1.8569</v>
@@ -844,13 +844,13 @@
         <v>0.579</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2082</v>
+        <v>0.0258</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0304</v>
+        <v>0.0697</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1778</v>
+        <v>-0.044</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.3412</v>
+        <v>-1.7274</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.3502</v>
+        <v>-1.7901</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0091</v>
+        <v>0.0626</v>
       </c>
       <c r="G6" t="n">
         <v>-0.6945</v>
@@ -922,13 +922,13 @@
         <v>2.3161</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3027</v>
+        <v>0.9165</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2353</v>
+        <v>0.7955</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0674</v>
+        <v>0.1209</v>
       </c>
       <c r="V6" t="n">
         <v>-0.9843</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.6782</v>
+        <v>-2.651</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1425</v>
+        <v>0.0185</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.5357</v>
+        <v>-2.6695</v>
       </c>
       <c r="G7" t="n">
         <v>0.2862</v>
@@ -1000,13 +1000,13 @@
         <v>1.9301</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1937</v>
+        <v>1.2208</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2102</v>
+        <v>0.9509</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4038</v>
+        <v>0.27</v>
       </c>
       <c r="V7" t="n">
         <v>-1.842</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.8724</v>
+        <v>-2.9513</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.0772</v>
+        <v>-1.5577</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.7952</v>
+        <v>-1.3936</v>
       </c>
       <c r="G8" t="n">
         <v>-0.7221</v>
@@ -1078,13 +1078,13 @@
         <v>2.3161</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9802</v>
+        <v>-0.0592</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2353</v>
+        <v>0.7549</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.2156</v>
+        <v>-0.8139999999999999</v>
       </c>
       <c r="V8" t="n">
         <v>-2.1701</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.3638</v>
+        <v>-3.8562</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.97</v>
+        <v>-1.5694</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.3939</v>
+        <v>-2.2868</v>
       </c>
       <c r="G9" t="n">
         <v>-1.9548</v>
@@ -1156,13 +1156,13 @@
         <v>0.772</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3741</v>
+        <v>0.1335</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1044</v>
+        <v>0.2961</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2697</v>
+        <v>-0.1626</v>
       </c>
       <c r="V9" t="n">
         <v>-1.842</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.8889</v>
+        <v>-5.9014</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.5963</v>
+        <v>-4.6355</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2927</v>
+        <v>-1.2659</v>
       </c>
       <c r="G10" t="n">
         <v>-5.8255</v>
@@ -1234,13 +1234,13 @@
         <v>2.3161</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1368</v>
+        <v>1.1243</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5764</v>
+        <v>1.5372</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4396</v>
+        <v>-0.4128</v>
       </c>
       <c r="V10" t="n">
         <v>-0.0422</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-12.2396</v>
+        <v>-11.6448</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.4653000000000009</v>
+        <v>0.1294000000000004</v>
       </c>
       <c r="F11" t="n">
-        <v>-11.7744</v>
+        <v>-11.7743</v>
       </c>
       <c r="G11" t="n">
         <v>-8.0029</v>
@@ -1312,10 +1312,10 @@
         <v>16.4057</v>
       </c>
       <c r="S11" t="n">
-        <v>7.8658</v>
+        <v>8.460599999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>8.811</v>
+        <v>9.4061</v>
       </c>
       <c r="U11" t="n">
         <v>-0.9455</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.0077</v>
+        <v>7.3693</v>
       </c>
       <c r="E12" t="n">
-        <v>8.1044</v>
+        <v>8.9055</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.0967</v>
+        <v>-1.5362</v>
       </c>
       <c r="G12" t="n">
         <v>3.4736</v>
@@ -1390,13 +1390,13 @@
         <v>4.0532</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.5937</v>
+        <v>-1.2321</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.4277</v>
+        <v>-0.6266</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.166</v>
+        <v>-0.6055</v>
       </c>
       <c r="V12" t="n">
         <v>3.9698</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.7423</v>
+        <v>5.7973</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9211</v>
+        <v>3.5219</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8212</v>
+        <v>2.2753</v>
       </c>
       <c r="G13" t="n">
         <v>4.1421</v>
@@ -1468,13 +1468,13 @@
         <v>3.8602</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.3299</v>
+        <v>-0.275</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3437</v>
+        <v>0.2572</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9862</v>
+        <v>-0.5321</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. MARTÍN CASTAÑEDA</t>
+          <t>M. SOLORZANO COLSA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.8443</v>
+        <v>2.7759</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8196</v>
+        <v>1.1628</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0247</v>
+        <v>1.6131</v>
       </c>
       <c r="G14" t="n">
-        <v>1.2938</v>
+        <v>2.8396</v>
       </c>
       <c r="H14" t="n">
-        <v>1.2431</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0507</v>
+        <v>1.8572</v>
       </c>
       <c r="J14" t="n">
-        <v>1.9008</v>
+        <v>2.2724</v>
       </c>
       <c r="K14" t="n">
-        <v>1.6973</v>
+        <v>1.0764</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2035</v>
+        <v>1.196</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.6071</v>
+        <v>0.5672</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4542</v>
+        <v>-0.094</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1528</v>
+        <v>0.6612</v>
       </c>
       <c r="P14" t="n">
-        <v>1.5441</v>
+        <v>-0.193</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-2.8951</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5441</v>
+        <v>2.7021</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1864</v>
+        <v>-0.3047</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9188</v>
+        <v>0.2717</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7324000000000001</v>
+        <v>-0.5764</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.18</v>
+        <v>0.434</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.5138</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.18</v>
+        <v>-1.0798</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. SOLORZANO COLSA</t>
+          <t>A. MARTÍN CASTAÑEDA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.7898</v>
+        <v>2.491</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7636</v>
+        <v>2.1186</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0261</v>
+        <v>0.3723</v>
       </c>
       <c r="G15" t="n">
-        <v>2.8396</v>
+        <v>1.2938</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9824000000000001</v>
+        <v>1.2431</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8572</v>
+        <v>0.0507</v>
       </c>
       <c r="J15" t="n">
-        <v>2.2724</v>
+        <v>1.9008</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0764</v>
+        <v>1.6973</v>
       </c>
       <c r="L15" t="n">
-        <v>1.196</v>
+        <v>0.2035</v>
       </c>
       <c r="M15" t="n">
-        <v>0.5672</v>
+        <v>-0.6071</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.094</v>
+        <v>-0.4542</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6612</v>
+        <v>-0.1528</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.193</v>
+        <v>1.5441</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.8951</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.7021</v>
+        <v>1.5441</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2908</v>
+        <v>-0.1669</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8725000000000001</v>
+        <v>0.2178</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.1634</v>
+        <v>-0.3847</v>
       </c>
       <c r="V15" t="n">
-        <v>0.434</v>
+        <v>-0.18</v>
       </c>
       <c r="W15" t="n">
-        <v>1.5138</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0798</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1867</v>
+        <v>1.8664</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8588</v>
+        <v>1.4583</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3279</v>
+        <v>0.4082</v>
       </c>
       <c r="G16" t="n">
         <v>2.0414</v>
@@ -1702,13 +1702,13 @@
         <v>0.386</v>
       </c>
       <c r="S16" t="n">
-        <v>0.06809999999999999</v>
+        <v>-0.2522</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5486</v>
+        <v>0.1481</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4805</v>
+        <v>-0.4002</v>
       </c>
       <c r="V16" t="n">
         <v>0.6562</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1291</v>
+        <v>0.4073</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0404</v>
+        <v>-0.8415</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1695</v>
+        <v>1.2488</v>
       </c>
       <c r="G17" t="n">
         <v>-1.1816</v>
@@ -1780,13 +1780,13 @@
         <v>2.1231</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3749</v>
+        <v>0.6531</v>
       </c>
       <c r="T17" t="n">
-        <v>1.4674</v>
+        <v>0.6663</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0926</v>
+        <v>-0.0132</v>
       </c>
       <c r="V17" t="n">
         <v>-0.2222</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. RUIZ FERNÁNDEZ</t>
+          <t>J. TEJERINA TEJEDO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7026</v>
+        <v>-0.0398</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5417</v>
+        <v>1.2974</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1608</v>
+        <v>-1.3373</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5125</v>
+        <v>0.2199</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1615</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.674</v>
+        <v>0.2913</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6262</v>
+        <v>1.7745</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0414</v>
+        <v>0.3828</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6676</v>
+        <v>1.3916</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1137</v>
+        <v>-1.5546</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1201</v>
+        <v>-0.4542</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0064</v>
+        <v>-1.1003</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.579</v>
+        <v>0.772</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R18" t="n">
-        <v>0.386</v>
+        <v>2.7021</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.659</v>
+        <v>-0.1742</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1785</v>
+        <v>0.2251</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4805</v>
+        <v>-0.3993</v>
       </c>
       <c r="V18" t="n">
-        <v>1.048</v>
+        <v>-0.8576</v>
       </c>
       <c r="W18" t="n">
         <v>1.228</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.18</v>
+        <v>-2.0856</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. TEJERINA TEJEDO</t>
+          <t>A. RUIZ FERNÁNDEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8479</v>
+        <v>-0.2885</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5964</v>
+        <v>-0.3415</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4444</v>
+        <v>0.053</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2199</v>
+        <v>-0.5125</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.07140000000000001</v>
+        <v>0.1615</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2913</v>
+        <v>-0.674</v>
       </c>
       <c r="J19" t="n">
-        <v>1.7745</v>
+        <v>-0.6262</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3828</v>
+        <v>0.0414</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3916</v>
+        <v>-0.6676</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.5546</v>
+        <v>0.1137</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4542</v>
+        <v>0.1201</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.1003</v>
+        <v>-0.0064</v>
       </c>
       <c r="P19" t="n">
-        <v>0.772</v>
+        <v>-0.579</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R19" t="n">
-        <v>2.7021</v>
+        <v>0.386</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9822</v>
+        <v>-0.2449</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4759</v>
+        <v>0.0218</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5063</v>
+        <v>-0.2667</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.8576</v>
+        <v>1.048</v>
       </c>
       <c r="W19" t="n">
         <v>1.228</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.0856</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.558</v>
+        <v>-1.8438</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.013</v>
+        <v>-3.9128</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4549</v>
+        <v>2.069</v>
       </c>
       <c r="G20" t="n">
         <v>-4.7823</v>
@@ -2014,13 +2014,13 @@
         <v>4.4392</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.4899</v>
+        <v>-0.7756999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0925</v>
+        <v>0.0076</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.3974</v>
+        <v>-0.7833</v>
       </c>
       <c r="V20" t="n">
         <v>2.1701</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.3516</v>
+        <v>-2.2897</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6946</v>
+        <v>-1.5944</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.657</v>
+        <v>-0.6953</v>
       </c>
       <c r="G21" t="n">
         <v>0.4688</v>
@@ -2092,13 +2092,13 @@
         <v>1.9301</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.1495</v>
+        <v>-1.0877</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3437</v>
+        <v>-0.2435</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.8058</v>
+        <v>-0.8441</v>
       </c>
       <c r="V21" t="n">
         <v>-2.6359</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>12.2398</v>
+        <v>16.2454</v>
       </c>
       <c r="E22" t="n">
-        <v>11.7742</v>
+        <v>11.7743</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4654000000000003</v>
+        <v>4.4709</v>
       </c>
       <c r="G22" t="n">
         <v>8.002800000000001</v>
@@ -2170,13 +2170,13 @@
         <v>24.1261</v>
       </c>
       <c r="S22" t="n">
-        <v>-7.865600000000001</v>
+        <v>-3.8603</v>
       </c>
       <c r="T22" t="n">
-        <v>0.9453000000000004</v>
+        <v>0.9455</v>
       </c>
       <c r="U22" t="n">
-        <v>-8.8111</v>
+        <v>-4.805499999999999</v>
       </c>
       <c r="V22" t="n">
         <v>4.382400000000001</v>
